--- a/assets/files/data_siswa.xlsx
+++ b/assets/files/data_siswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{312A1A07-EE61-4428-9428-169D62042322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28F140C-1876-49ED-8652-4A4169D4F41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1821EDD2-D48C-4B63-B11F-0F4051BEE17D}"/>
   </bookViews>
@@ -144,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,6 +162,12 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -479,6 +485,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF291F1-A30E-4B5B-B637-8F2C3DF695FC}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -495,13 +507,13 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="5">
@@ -509,13 +521,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4">
@@ -523,13 +535,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="4">
@@ -537,13 +549,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4">
@@ -551,13 +563,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="4">
@@ -565,13 +577,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="4">
@@ -579,13 +591,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="4">
@@ -593,13 +605,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4">
@@ -607,13 +619,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="4">
@@ -621,13 +633,13 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="4">

--- a/assets/files/data_siswa.xlsx
+++ b/assets/files/data_siswa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28F140C-1876-49ED-8652-4A4169D4F41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD92B751-6118-4C4F-B93A-2F3984F445DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1821EDD2-D48C-4B63-B11F-0F4051BEE17D}"/>
   </bookViews>
@@ -99,7 +99,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,7 +117,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -149,24 +154,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -187,9 +190,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -227,7 +230,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -333,7 +336,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,7 +478,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -486,10 +489,11 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="6" customWidth="1"/>
+    <col min="4" max="5" width="11.28515625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -502,152 +506,152 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="8">
         <v>85.5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>78.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>92.75</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>88.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>76.25</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>84.75</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>87.25</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>79.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <f>SUM(D2:D11)</f>
         <v>842.75</v>
       </c>
